--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/tester-types-easy.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/tester-types-easy.xlsx
@@ -460,19 +460,19 @@
         <v>Kiểm thử tĩnh (Static Testing) bao gồm duyệt tài liệu yêu cầu, duyệt code (code review) để tìm lỗi logic/cú pháp mà không chạy phần mềm. Kiểm thử động (Dynamic Testing) bắt buộc phải nạp code chạy thực tế để đối chiếu kết quả.</v>
       </c>
       <c r="F2" t="str">
+        <v>Kiểm thử tĩnh do QA thực hiện; Kiểm thử động do lập trình viên tự thực hiện trên máy chủ — phân chia vai trò</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Kiểm thử tĩnh hoàn toàn miễn phí; Kiểm thử động yêu cầu phải mua bản quyền phần mềm đắt tiền — so sánh chi phí</v>
+      </c>
+      <c r="H2" t="str">
         <v>Kiểm thử tĩnh kiểm tra tài liệu, mã nguồn mà không chạy chương trình (như review, walkthrough); Kiểm thử động yêu cầu chạy phần mềm để kiểm tra hành vi — không chạy code vs chạy code</v>
       </c>
-      <c r="G2" t="str">
+      <c r="I2" t="str">
         <v>Kiểm thử tĩnh chỉ áp dụng cho trang web tĩnh HTML; Kiểm thử động áp dụng cho trang web có hoạt ảnh CSS — phân loại theo hiệu ứng</v>
       </c>
-      <c r="H2" t="str">
-        <v>Kiểm thử tĩnh do QA thực hiện; Kiểm thử động do lập trình viên tự thực hiện trên máy chủ — phân chia vai trò</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Kiểm thử tĩnh hoàn toàn miễn phí; Kiểm thử động yêu cầu phải mua bản quyền phần mềm đắt tiền — so sánh chi phí</v>
-      </c>
       <c r="J2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -492,19 +492,19 @@
         <v>Smoke Test (hoặc Build Verification Test) chạy nhanh một bộ test case cơ bản (như đăng nhập, mở trang chủ) để quyết định xem bản build này có đủ ổn định để đội test nhận vào chạy các bộ test chi tiết hay không, tránh lãng phí thời gian nếu bản build bị lỗi sập nguồn ngay lập tức.</v>
       </c>
       <c r="F3" t="str">
-        <v>Thực hiện ngay khi nhận bản build mới để nhanh chóng xác nhận các chức năng cốt lõi nhất có hoạt động bình thường không trước khi test chi tiết — kiểm tra bản build ổn định cơ bản</v>
+        <v>Chỉ thực hiện khi hệ thống cơ sở dữ liệu bị sập hoàn toàn và không thể truy cập được — xử lý sự cố database</v>
       </c>
       <c r="G3" t="str">
         <v>Thực hiện vào cuối dự án để kiểm tra xem hệ thống máy chủ có bị bốc khói do quá tải hay không — kiểm tra nhiệt độ máy chủ</v>
       </c>
       <c r="H3" t="str">
+        <v>Thực hiện ngay khi nhận bản build mới để nhanh chóng xác nhận các chức năng cốt lõi nhất có hoạt động bình thường không trước khi test chi tiết — kiểm tra bản build ổn định cơ bản</v>
+      </c>
+      <c r="I3" t="str">
         <v>Thực hiện trên môi trường của khách hàng để hướng dẫn họ cách cài đặt ứng dụng di động — hướng dẫn cài đặt</v>
       </c>
-      <c r="I3" t="str">
-        <v>Chỉ thực hiện khi hệ thống cơ sở dữ liệu bị sập hoàn toàn và không thể truy cập được — xử lý sự cố database</v>
-      </c>
       <c r="J3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -524,19 +524,19 @@
         <v>Integration Testing (Kiểm thử tích hợp) tập trung kiểm tra giao tiếp, truyền tải dữ liệu (interfaces) giữa các thành phần phần mềm hoặc giữa các hệ thống với nhau.</v>
       </c>
       <c r="F4" t="str">
+        <v>System Testing — Kiểm thử toàn bộ hệ thống hoàn chỉnh từ đầu đến cuối — mức độ hệ thống</v>
+      </c>
+      <c r="G4" t="str">
         <v>Integration Testing — Kiểm thử tích hợp — mức độ tích hợp</v>
       </c>
-      <c r="G4" t="str">
+      <c r="H4" t="str">
+        <v>Acceptance Testing — Kiểm thử chấp nhận người dùng nghiệm thu sản phẩm — mức độ nghiệm thu</v>
+      </c>
+      <c r="I4" t="str">
         <v>Unit Testing — Kiểm thử đơn vị các hàm, phương thức nhỏ trong code — mức độ đơn vị</v>
       </c>
-      <c r="H4" t="str">
-        <v>System Testing — Kiểm thử toàn bộ hệ thống hoàn chỉnh từ đầu đến cuối — mức độ hệ thống</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Acceptance Testing — Kiểm thử chấp nhận người dùng nghiệm thu sản phẩm — mức độ nghiệm thu</v>
-      </c>
       <c r="J4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -556,19 +556,19 @@
         <v>Functional testing validate các yêu cầu chức năng (đăng nhập, thanh toán). Non-functional testing validate chất lượng vận hành của hệ thống (tốc độ tải trang, khả năng chịu tải, tính bảo mật thông tin).</v>
       </c>
       <c r="F5" t="str">
+        <v>Chức năng chỉ test trên máy tính; Phi chức năng chỉ test trên điện thoại di động di động — phân loại thiết bị test</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Chức năng luôn luôn dễ phát hiện lỗi hơn gấp 10 lần so với phi chức năng — mức độ phát hiện lỗi</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Chức năng do lập trình viên tự test; Phi chức năng bắt buộc phải thuê bên thứ ba độc lập vào test — phân chia vai trò test</v>
+      </c>
+      <c r="I5" t="str">
         <v>Chức năng kiểm tra hệ thống làm ĐƯỢC GÌ (hành vi nghiệp vụ); Phi chức năng kiểm tra hệ thống chạy NHƯ THẾ NÀO (hiệu năng, bảo mật, tính khả dụng) — làm được gì vs chạy như thế nào</v>
       </c>
-      <c r="G5" t="str">
-        <v>Chức năng do lập trình viên tự test; Phi chức năng bắt buộc phải thuê bên thứ ba độc lập vào test — phân chia vai trò test</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Chức năng chỉ test trên máy tính; Phi chức năng chỉ test trên điện thoại di động di động — phân loại thiết bị test</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Chức năng luôn luôn dễ phát hiện lỗi hơn gấp 10 lần so với phi chức năng — mức độ phát hiện lỗi</v>
-      </c>
       <c r="J5">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -588,19 +588,19 @@
         <v>Unit Testing đòi hỏi đọc hiểu cấu trúc code ở cấp độ hàm/phương thức chi tiết (White-box testing), do đó lập trình viên phải tự viết các unit test cases (ví dụ dùng JUnit, NUnit, Jest) để chạy kiểm tra trước khi commit code.</v>
       </c>
       <c r="F6" t="str">
+        <v>Project Manager chịu trách nhiệm quản lý chung của dự án — quản lý dự án</v>
+      </c>
+      <c r="G6" t="str">
         <v>Developer (Lập trình viên) trực tiếp viết code của dự án — lập trình viên thực hiện</v>
       </c>
-      <c r="G6" t="str">
+      <c r="H6" t="str">
         <v>Manual QA (Kiểm thử viên thủ công) chuyên viết test case trên Excel — kiểm thử viên thủ công</v>
       </c>
-      <c r="H6" t="str">
+      <c r="I6" t="str">
         <v>Khách hàng hoặc người dùng cuối ở giai đoạn nghiệm thu bàn giao — người dùng cuối</v>
       </c>
-      <c r="I6" t="str">
-        <v>Project Manager chịu trách nhiệm quản lý chung của dự án — quản lý dự án</v>
-      </c>
       <c r="J6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -623,13 +623,13 @@
         <v>Hiểu rõ yêu cầu nghiệp vụ và hành vi bên ngoài của hệ thống mà không cần quan tâm đến cấu trúc code bên trong — hiểu nghiệp vụ hành vi</v>
       </c>
       <c r="G7" t="str">
+        <v>Biết cách cấu hình hệ thống mạng và cài đặt máy chủ vật lý cho công ty — cấu hình máy chủ</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Biết cách thiết kế giao diện đồ họa bằng công cụ Figma hoặc Adobe Photoshop — đồ họa giao diện</v>
+      </c>
+      <c r="I7" t="str">
         <v>Đọc hiểu chi tiết mã nguồn code Java/C# và cấu trúc thuật toán của dev — đọc hiểu mã nguồn</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Biết cách cấu hình hệ thống mạng và cài đặt máy chủ vật lý cho công ty — cấu hình máy chủ</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Biết cách thiết kế giao diện đồ họa bằng công cụ Figma hoặc Adobe Photoshop — đồ họa giao diện</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -655,10 +655,10 @@
         <v>Acceptance Testing — Kiểm thử chấp nhận (nghiệm thu) — mức độ nghiệm thu</v>
       </c>
       <c r="G8" t="str">
+        <v>Integration Testing — Kiểm thử tích hợp các module — mức độ tích hợp</v>
+      </c>
+      <c r="H8" t="str">
         <v>System Testing — Kiểm thử toàn bộ hệ thống tích hợp — mức độ hệ thống</v>
-      </c>
-      <c r="H8" t="str">
-        <v>Integration Testing — Kiểm thử tích hợp các module — mức độ tích hợp</v>
       </c>
       <c r="I8" t="str">
         <v>Unit Testing — Kiểm thử đơn vị các thành phần code — mức độ đơn vị</v>
@@ -684,19 +684,19 @@
         <v>Khi sửa code, dev dễ vô tình làm hỏng logic của các phần khác (side effects). Regression testing chạy lại một bộ test case ở các khu vực liên quan để đảm bảo tính ổn định của hệ thống.</v>
       </c>
       <c r="F9" t="str">
+        <v>Kiểm tra xem hệ thống có bị hack thông qua các cổng mạng đang mở hay không — kiểm thử bảo mật</v>
+      </c>
+      <c r="G9" t="str">
         <v>Đảm bảo các thay đổi mới (sửa lỗi, thêm tính năng) không gây ảnh hưởng xấu (tạo ra lỗi mới) ở các vùng chức năng cũ đang hoạt động ổn định — ngăn chặn tác động phụ</v>
       </c>
-      <c r="G9" t="str">
-        <v>Kiểm tra xem hệ thống có bị hack thông qua các cổng mạng đang mở hay không — kiểm thử bảo mật</v>
-      </c>
       <c r="H9" t="str">
+        <v>Đo lường thời gian phản hồi của trang web khi có đúng 1 người dùng truy cập — kiểm thử hiệu năng tối thiểu</v>
+      </c>
+      <c r="I9" t="str">
         <v>Tính toán tổng số tiền tối đa doanh nghiệp có thể tiết kiệm được nhờ áp dụng phần mềm — tính toán lợi nhuận</v>
       </c>
-      <c r="I9" t="str">
-        <v>Đo lường thời gian phản hồi của trang web khi có đúng 1 người dùng truy cập — kiểm thử hiệu năng tối thiểu</v>
-      </c>
       <c r="J9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -716,19 +716,19 @@
         <v>White-box testing (hoặc Glass-box/Clear-box) yêu cầu nhìn thấy bên trong hộp (code). Tester thiết kế kịch bản test để phủ hết các dòng lệnh, các rẽ nhánh IF-ELSE của thuật toán.</v>
       </c>
       <c r="F10" t="str">
+        <v>Tài liệu kế hoạch ngân sách tài chính của dự án phát triển phần mềm — kế hoạch tài chính</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Độ hài lòng của khách hàng sau khi dùng thử sản phẩm trong 1 tuần — độ hài lòng khách hàng</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Giao diện người dùng bên ngoài bao gồm hình ảnh, màu sắc và font chữ — giao diện bên ngoài</v>
+      </c>
+      <c r="I10" t="str">
         <v>Cấu trúc logic bên trong, các đường dẫn thực thi câu lệnh (branches, paths) và mã nguồn của phần mềm — cấu trúc code logic bên trong</v>
       </c>
-      <c r="G10" t="str">
-        <v>Giao diện người dùng bên ngoài bao gồm hình ảnh, màu sắc và font chữ — giao diện bên ngoài</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Độ hài lòng của khách hàng sau khi dùng thử sản phẩm trong 1 tuần — độ hài lòng khách hàng</v>
-      </c>
-      <c r="I10" t="str">
-        <v>Tài liệu kế hoạch ngân sách tài chính của dự án phát triển phần mềm — kế hoạch tài chính</v>
-      </c>
       <c r="J10">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -748,19 +748,19 @@
         <v>Usability testing đánh giá xem người dùng có dễ dàng học cách dùng app không, thao tác có bị bối rối không, từ đó tối ưu trải nghiệm người dùng (UX).</v>
       </c>
       <c r="F11" t="str">
-        <v>Mức độ dễ sử dụng, thân thiện của giao diện và mức độ hài lòng của người dùng khi tương tác — tính dễ dùng và thân thiện</v>
+        <v>Số lượng bản ghi tối đa cơ sở dữ liệu có thể lưu trữ trong một giây — hiệu năng database</v>
       </c>
       <c r="G11" t="str">
         <v>Mức độ an toàn bảo mật trước các cuộc tấn công từ chối dịch vụ DDoS — bảo mật hệ thống</v>
       </c>
       <c r="H11" t="str">
-        <v>Số lượng bản ghi tối đa cơ sở dữ liệu có thể lưu trữ trong một giây — hiệu năng database</v>
+        <v>Số năm sử dụng tối đa của hệ thống máy chủ trước khi bị hỏng — tuổi thọ máy chủ</v>
       </c>
       <c r="I11" t="str">
-        <v>Số năm sử dụng tối đa của hệ thống máy chủ trước khi bị hỏng — tuổi thọ máy chủ</v>
+        <v>Mức độ dễ sử dụng, thân thiện của giao diện và mức độ hài lòng của người dùng khi tương tác — tính dễ dùng và thân thiện</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
